--- a/데모데이터/가상주문_연구소_2026-10.xlsx
+++ b/데모데이터/가상주문_연구소_2026-10.xlsx
@@ -9,15 +9,65 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <cellXfs count="2">
-    <xf numFmtId="0"/>
-    <xf numFmtId="14"/>
+  <fonts count="2">
+    <font>
+      <sz val="11"/>
+      <name val="Malgun Gothic"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Malgun Gothic"/>
+    </font>
+  </fonts>
+  <fills count="2">
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+  </fills>
+  <borders count="1">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+  </borders>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
 </styleSheet>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="9" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="10" customWidth="1"/>
+    <col min="11" max="11" width="10" customWidth="1"/>
+    <col min="12" max="12" width="14" customWidth="1"/>
+    <col min="13" max="13" width="26" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -34,67 +84,67 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="inlineStr" s="2">
         <is>
           <t>발주번호</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" t="inlineStr" s="2">
         <is>
           <t>품명</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" t="inlineStr" s="2">
         <is>
           <t>거래처</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" t="inlineStr" s="2">
         <is>
           <t>신청자</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" t="inlineStr" s="2">
         <is>
           <t>발주일</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" t="inlineStr" s="2">
         <is>
           <t>납기예정일</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" t="inlineStr" s="2">
         <is>
           <t>선적</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" t="inlineStr" s="2">
         <is>
           <t>통관</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" t="inlineStr" s="2">
         <is>
           <t>발주수량</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" t="inlineStr" s="2">
         <is>
           <t>누적입고</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" t="inlineStr" s="2">
         <is>
           <t>입고확인</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L3" t="inlineStr" s="2">
         <is>
           <t>모델/규격</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M3" t="inlineStr" s="2">
         <is>
           <t>비고</t>
         </is>
